--- a/data/merged/2026-10-08/MERGED_IT_Robot-Vacuum_2026-10-08.xlsx
+++ b/data/merged/2026-10-08/MERGED_IT_Robot-Vacuum_2026-10-08.xlsx
@@ -5042,50 +5042,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="28" name="Product 28">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId28" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -5411,7 +5367,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR51"/>
+  <dimension ref="A1:BR50"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -16844,224 +16800,6 @@
       <c r="BP50" s="23"/>
       <c r="BQ50" s="23"/>
       <c r="BR50" s="13"/>
-    </row>
-    <row r="51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="13">
-        <v>50</v>
-      </c>
-      <c r="B51" s="13"/>
-      <c r="C51" s="14" t="inlineStr">
-        <is>
-          <t>B0C78DVSYP</t>
-        </is>
-      </c>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14" t="inlineStr">
-        <is>
-          <t>dreame</t>
-        </is>
-      </c>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/stores/DREAME/page/6460262E-9E3A-415B-B395-83EC96AB6666?lp_asin=B0C78DVSYP&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
-        </is>
-      </c>
-      <c r="H51" s="14" t="inlineStr">
-        <is>
-          <t>DREAME 4x Panni mocio di ricambio(×2 Paia) compatibili con X40Master/L10sUltraGen2/L50ProUltra/X50Master/L40sProUltra/L40Ultr</t>
-        </is>
-      </c>
-      <c r="I51" s="14"/>
-      <c r="J51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/dp/B0C78DVSYP?psc=1</t>
-        </is>
-      </c>
-      <c r="K51" s="14" t="inlineStr">
-        <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71wCGkM+anL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L51" s="14" t="inlineStr">
-        <is>
-          <t>B0C78DVSYP</t>
-        </is>
-      </c>
-      <c r="M51" s="14" t="inlineStr">
-        <is>
-          <t>Casa e cucina:Aspirapolvere e pulizia di pavimenti e finestre:Aspirapolvere:Aspirapolvere robot</t>
-        </is>
-      </c>
-      <c r="N51" s="14" t="inlineStr">
-        <is>
-          <t>Visualizza i Top 100 nella categoria Casa e c</t>
-        </is>
-      </c>
-      <c r="O51" s="15">
-        <v>1071</v>
-      </c>
-      <c r="P51" s="15">
-        <v>5859</v>
-      </c>
-      <c r="Q51" s="16">
-        <v>0.85</v>
-      </c>
-      <c r="R51" s="17" t="inlineStr">
-        <is>
-          <t>Aspirapolvere robot</t>
-        </is>
-      </c>
-      <c r="S51" s="18" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="T51" s="15">
-        <v>242</v>
-      </c>
-      <c r="U51" s="16">
-        <v>1.14</v>
-      </c>
-      <c r="V51" s="15">
-        <v>2418</v>
-      </c>
-      <c r="W51" s="15" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="X51" s="15">
-        <v>1791</v>
-      </c>
-      <c r="Y51" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z51" s="20">
-        <v>8.19</v>
-      </c>
-      <c r="AA51"/>
-      <c r="AB51"/>
-      <c r="AC51" s="2"/>
-      <c r="AD51" s="19">
-        <v>611</v>
-      </c>
-      <c r="AE51" s="15">
-        <v>13</v>
-      </c>
-      <c r="AF51" s="21">
-        <v>4.6</v>
-      </c>
-      <c r="AG51" s="22">
-        <v>0.0537</v>
-      </c>
-      <c r="AH51" s="20">
-        <v>3.64</v>
-      </c>
-      <c r="AI51" s="16">
-        <v>0.49</v>
-      </c>
-      <c r="AJ51"/>
-      <c r="AK51" s="13" t="inlineStr">
-        <is>
-          <t>2023-06-07</t>
-        </is>
-      </c>
-      <c r="AL51" s="19">
-        <v>1218</v>
-      </c>
-      <c r="AM51" s="13" t="inlineStr">
-        <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AN51" s="13"/>
-      <c r="AO51" s="13"/>
-      <c r="AP51"/>
-      <c r="AQ51" s="19">
-        <v>10</v>
-      </c>
-      <c r="AR51" s="19">
-        <v>4</v>
-      </c>
-      <c r="AS51" s="14" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="AT51" s="13" t="inlineStr">
-        <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU51" s="13"/>
-      <c r="AV51" s="14"/>
-      <c r="AW51" s="13"/>
-      <c r="AX51" s="13"/>
-      <c r="AY51" s="13"/>
-      <c r="AZ51" s="13"/>
-      <c r="BA51" s="13"/>
-      <c r="BB51" s="13"/>
-      <c r="BC51" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD51" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BE51" s="13"/>
-      <c r="BF51" s="13"/>
-      <c r="BG51" s="13"/>
-      <c r="BH51" s="14"/>
-      <c r="BI51" s="23"/>
-      <c r="BJ51" s="23" t="inlineStr">
-        <is>
-          <t>40 g</t>
-        </is>
-      </c>
-      <c r="BK51" s="23" t="inlineStr">
-        <is>
-          <t>40.00 g</t>
-        </is>
-      </c>
-      <c r="BL51" s="23" t="inlineStr">
-        <is>
-          <t>15 x 15 x 15 cm</t>
-        </is>
-      </c>
-      <c r="BM51" s="23" t="inlineStr">
-        <is>
-          <t>15.00 x 15.00 x 15.00 cm</t>
-        </is>
-      </c>
-      <c r="BN51" s="23" t="inlineStr">
-        <is>
-          <t>70 g</t>
-        </is>
-      </c>
-      <c r="BO51" s="23" t="inlineStr">
-        <is>
-          <t>70.00 g</t>
-        </is>
-      </c>
-      <c r="BP51" s="23" t="inlineStr">
-        <is>
-          <t>14.5 x 14.4 x 4.2 cm</t>
-        </is>
-      </c>
-      <c r="BQ51" s="23" t="inlineStr">
-        <is>
-          <t>14.50 x 14.40 x 4.20 cm</t>
-        </is>
-      </c>
-      <c r="BR51" s="13" t="inlineStr">
-        <is>
-          <t>超大号信封</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -17434,15 +17172,8 @@
     <hyperlink ref="M50" r:id="rId365" tooltip="https://www.amazon.it/b?node=733026031"/>
     <hyperlink ref="N50" r:id="rId366"/>
     <hyperlink ref="AW50" r:id="rId367" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A16CP4VXQRK1V0"/>
-    <hyperlink ref="C51" r:id="rId368" tooltip="https://www.amazon.it/dp/B0C78DVSYP"/>
-    <hyperlink ref="G51" r:id="rId369" tooltip="https://www.amazon.it/stores/DREAME/page/6460262E-9E3A-415B-B395-83EC96AB6666?lp_asin=B0C78DVSYP&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J51" r:id="rId370" tooltip="https://www.amazon.it/dp/B0C78DVSYP?psc=1"/>
-    <hyperlink ref="K51" r:id="rId371" tooltip="https://images-na.ssl-images-amazon.com/images/I/71wCGkM+anL._AC_US600_.jpg"/>
-    <hyperlink ref="L51" r:id="rId372" tooltip="https://www.amazon.it/dp/B0C78DVSYP"/>
-    <hyperlink ref="M51" r:id="rId373" tooltip="https://www.amazon.it/b?node=733026031"/>
-    <hyperlink ref="N51" r:id="rId374"/>
   </hyperlinks>
-  <drawing r:id="rId375"/>
+  <drawing r:id="rId368"/>
 </worksheet>
 </file>
 
@@ -17501,18 +17232,18 @@
         </is>
       </c>
       <c r="B2" s="15">
-        <v>11319</v>
+        <v>11077</v>
       </c>
       <c r="C2" s="15">
-        <v>6064082</v>
+        <v>6061664</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
       <c r="F2" s="20">
-        <v>535.7436169272904</v>
+        <v>547.2297553489212</v>
       </c>
       <c r="G2" s="22">
-        <v>0.3418707904195234</v>
+        <v>0.33702497946268295</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17533,7 +17264,7 @@
         <v>517.7391158740791</v>
       </c>
       <c r="G3" s="22">
-        <v>0.18037391645776074</v>
+        <v>0.1817020111357897</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17554,7 +17285,7 @@
         <v>425.24298128342247</v>
       </c>
       <c r="G4" s="22">
-        <v>0.1807363556736839</v>
+        <v>0.18206711899473635</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17575,7 +17306,7 @@
         <v>573.8969834945931</v>
       </c>
       <c r="G5" s="22">
-        <v>0.05306714186474976</v>
+        <v>0.05345787568077403</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17596,7 +17327,7 @@
         <v>236.06668452062132</v>
       </c>
       <c r="G6" s="22">
-        <v>0.11277900268809085</v>
+        <v>0.11360939544223689</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17617,7 +17348,7 @@
         <v>280.89611809732094</v>
       </c>
       <c r="G7" s="22">
-        <v>0.055241777160288746</v>
+        <v>0.05564852283445401</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17638,7 +17369,7 @@
         <v>289.98972602739724</v>
       </c>
       <c r="G8" s="22">
-        <v>0.017638708508260593</v>
+        <v>0.01776858246873764</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17659,7 +17390,7 @@
         <v>843.0</v>
       </c>
       <c r="G9" s="22">
-        <v>0.0042586607870971635</v>
+        <v>0.0042900173426233</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17680,7 +17411,7 @@
         <v>138.12401883830455</v>
       </c>
       <c r="G10" s="22">
-        <v>0.01923948171192123</v>
+        <v>0.019381142179085403</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17701,7 +17432,7 @@
         <v>583.0</v>
       </c>
       <c r="G11" s="22">
-        <v>0.0034733758192636442</v>
+        <v>0.0034989503149055285</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17722,7 +17453,7 @@
         <v>76.89958158995816</v>
       </c>
       <c r="G12" s="22">
-        <v>0.014437162100939321</v>
+        <v>0.01454346304804211</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17743,7 +17474,7 @@
         <v>171.74358974358975</v>
       </c>
       <c r="G13" s="22">
-        <v>0.005889637258751397</v>
+        <v>0.005933002707883287</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17764,7 +17495,7 @@
         <v>169.98930481283423</v>
       </c>
       <c r="G14" s="22">
-        <v>0.005648011114802622</v>
+        <v>0.005689597468585511</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17785,7 +17516,7 @@
         <v>129.99180327868854</v>
       </c>
       <c r="G15" s="22">
-        <v>0.0036847986952188226</v>
+        <v>0.0037119298992910822</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17806,7 +17537,7 @@
         <v>82.98181818181818</v>
       </c>
       <c r="G16" s="22">
-        <v>0.0016611797396478298</v>
+        <v>0.0016734110201722093</v>
       </c>
     </row>
   </sheetData>
@@ -17870,18 +17601,18 @@
         </is>
       </c>
       <c r="B2" s="15">
-        <v>9722</v>
+        <v>9480</v>
       </c>
       <c r="C2" s="15">
-        <v>4517995</v>
+        <v>4515577</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
       <c r="F2" s="20">
-        <v>464.7186792840979</v>
+        <v>476.3266877637131</v>
       </c>
       <c r="G2" s="22">
-        <v>0.29363617143374915</v>
+        <v>0.2884352085678644</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17902,7 +17633,7 @@
         <v>425.24298128342247</v>
       </c>
       <c r="G3" s="22">
-        <v>0.1807363556736839</v>
+        <v>0.18206711899473635</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17923,7 +17654,7 @@
         <v>494.7964166174444</v>
       </c>
       <c r="G4" s="22">
-        <v>0.1534023981394787</v>
+        <v>0.15453190129917546</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17944,7 +17675,7 @@
         <v>709.0</v>
       </c>
       <c r="G5" s="22">
-        <v>0.10302334712615906</v>
+        <v>0.10378190890558919</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17965,7 +17696,7 @@
         <v>349.2713321055862</v>
       </c>
       <c r="G6" s="22">
-        <v>0.14760337068470808</v>
+        <v>0.14869017555602884</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17986,7 +17717,7 @@
         <v>236.06668452062132</v>
       </c>
       <c r="G7" s="22">
-        <v>0.11277900268809085</v>
+        <v>0.11360939544223689</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18007,7 +17738,7 @@
         <v>583.0</v>
       </c>
       <c r="G8" s="22">
-        <v>0.0034733758192636442</v>
+        <v>0.0034989503149055285</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18028,7 +17759,7 @@
         <v>129.99180327868854</v>
       </c>
       <c r="G9" s="22">
-        <v>0.0036847986952188226</v>
+        <v>0.0037119298992910822</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18049,7 +17780,7 @@
         <v>82.98181818181818</v>
       </c>
       <c r="G10" s="22">
-        <v>0.0016611797396478298</v>
+        <v>0.0016734110201722093</v>
       </c>
     </row>
   </sheetData>
